--- a/artfynd/A 48891-2023 artfynd.xlsx
+++ b/artfynd/A 48891-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48891-2023 artfynd.xlsx
+++ b/artfynd/A 48891-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,65 +1055,69 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114598106</v>
+        <v>115477547</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
+        <v>97650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mantmosskogen, Ramnäs sn, Vstm</t>
+          <t>Mantestorp, väster vägen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562569</v>
+        <v>562816</v>
       </c>
       <c r="R5" t="n">
-        <v>6633154</v>
+        <v>6633156</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,22 +1141,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,145 +1155,27 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>115477547</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Mantestorp, väster vägen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>562816</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6633156</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48891-2023 artfynd.xlsx
+++ b/artfynd/A 48891-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87154299</v>
+        <v>335265</v>
       </c>
       <c r="B2" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mantmossen, Vstm</t>
+          <t>Mantestorp, 100 m V, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562561.9261150972</v>
+        <v>562798</v>
       </c>
       <c r="R2" t="n">
-        <v>6633162.000179252</v>
+        <v>6633176</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,91 +754,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>ås, gamla tallar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105612170</v>
+        <v>87154299</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mantmosskogen, Ramnäs sn, Vstm</t>
+          <t>Mantmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562568.112770069</v>
+        <v>562562</v>
       </c>
       <c r="R3" t="n">
-        <v>6633153.555979102</v>
+        <v>6633162</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,27 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I barkborreangripna granar</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,80 +860,74 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114598107</v>
+        <v>1559058</v>
       </c>
       <c r="B4" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mantmosskogen, Ramnäs sn, Vstm</t>
+          <t>Mantestorp, 100 m V, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562569</v>
+        <v>562798</v>
       </c>
       <c r="R4" t="n">
-        <v>6633154</v>
+        <v>6633176</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,85 +970,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>ås, gamla tallar</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115477547</v>
+        <v>123451864</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mantestorp, väster vägen, Vstm</t>
+          <t>Mantmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562816</v>
+        <v>562733</v>
       </c>
       <c r="R5" t="n">
-        <v>6633156</v>
+        <v>6633198</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,12 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,27 +1080,711 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1764350</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strömsholmsåsen, Mantestorp, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562718</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6633211</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-11-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-11-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grusås, gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105612170</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mantmosskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562569</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6633154</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-01-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-01-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I barkborreangripna granar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114598107</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mantmosskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562569</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6633154</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115477402</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mantesåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562784</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6633204</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115477547</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mantestorp, väster vägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562816</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6633156</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123452677</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mantmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562733</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6633198</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48891-2023 artfynd.xlsx
+++ b/artfynd/A 48891-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/335265</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87154299</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1559058</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1764350</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105612170</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114598107</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115477402</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115477547</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,8 +1835,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452677</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>